--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484171_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484171_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.552899999999999</v>
+        <v>9.551399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7815</v>
+        <v>6.6398</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7714</v>
+        <v>2.9117</v>
       </c>
       <c r="G2" t="n">
         <v>5.1982</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0935</v>
+        <v>-0.095</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4082</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6434</v>
+        <v>-0.5031</v>
       </c>
       <c r="V2" t="n">
         <v>1.4724</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.1271</v>
+        <v>7.9983</v>
       </c>
       <c r="E3" t="n">
-        <v>6.394</v>
+        <v>5.7421</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7332</v>
+        <v>2.2562</v>
       </c>
       <c r="G3" t="n">
         <v>5.6398</v>
@@ -688,13 +688,13 @@
         <v>3.3725</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9039</v>
+        <v>0.7751</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1678</v>
+        <v>0.5159</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7362</v>
+        <v>0.2592</v>
       </c>
       <c r="V3" t="n">
         <v>0.1947</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7669</v>
+        <v>6.989</v>
       </c>
       <c r="E4" t="n">
-        <v>2.24</v>
+        <v>4.5573</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5269</v>
+        <v>2.4317</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2717</v>
+        <v>5.6417</v>
       </c>
       <c r="H4" t="n">
-        <v>2.208</v>
+        <v>2.4287</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0637</v>
+        <v>3.2129</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6707</v>
+        <v>4.4682</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4297</v>
+        <v>1.9355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.241</v>
+        <v>2.5327</v>
       </c>
       <c r="M4" t="n">
-        <v>2.601</v>
+        <v>1.1734</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7783</v>
+        <v>0.4932</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8227</v>
+        <v>0.6802</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8207</v>
+        <v>-0.6688</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3548</v>
+        <v>-0.34</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5341</v>
+        <v>-0.3288</v>
       </c>
       <c r="V4" t="n">
-        <v>1.881</v>
+        <v>2.4129</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>2.4129</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2442</v>
+        <v>5.8611</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1492</v>
+        <v>1.4465</v>
       </c>
       <c r="F5" t="n">
-        <v>2.095</v>
+        <v>4.4147</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6417</v>
+        <v>3.2717</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4287</v>
+        <v>2.208</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2129</v>
+        <v>1.0637</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4682</v>
+        <v>0.6707</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9355</v>
+        <v>0.4297</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5327</v>
+        <v>0.241</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1734</v>
+        <v>2.601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4932</v>
+        <v>1.7783</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6802</v>
+        <v>0.8227</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4136</v>
+        <v>-0.0851</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7481</v>
+        <v>0.5612</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6655</v>
+        <v>-0.6463</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4129</v>
+        <v>1.881</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4129</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.0459</v>
+        <v>4.2348</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3978</v>
+        <v>1.0917</v>
       </c>
       <c r="F6" t="n">
-        <v>3.648</v>
+        <v>3.143</v>
       </c>
       <c r="G6" t="n">
         <v>4.3587</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>1.358</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6746</v>
+        <v>0.3685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6834</v>
+        <v>0.1784</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8692</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7058</v>
+        <v>2.6792</v>
       </c>
       <c r="E7" t="n">
-        <v>3.905</v>
+        <v>1.4618</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1992</v>
+        <v>1.2174</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8734</v>
+        <v>1.2772</v>
       </c>
       <c r="H7" t="n">
-        <v>1.784</v>
+        <v>0.3224</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.9548</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6636</v>
+        <v>1.0658</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5807</v>
+        <v>0.3831</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0.6827</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7902</v>
+        <v>0.2114</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7967</v>
+        <v>-0.0607</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0065</v>
+        <v>0.2721</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7855</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9918</v>
+        <v>0.3146</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2414</v>
+        <v>0.1814</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7504</v>
+        <v>0.1332</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.9449</v>
+        <v>1.881</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.9449</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2547</v>
+        <v>2.419</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0933</v>
+        <v>2.693</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1613</v>
+        <v>-0.274</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2772</v>
+        <v>3.1854</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3224</v>
+        <v>0.7511</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9548</v>
+        <v>2.4343</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0658</v>
+        <v>2.5003</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3831</v>
+        <v>0.6101</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6827</v>
+        <v>1.8901</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2114</v>
+        <v>0.6851</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0607</v>
+        <v>0.1409</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2721</v>
+        <v>0.5442</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.11</v>
+        <v>0.1785</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.187</v>
+        <v>0.1927</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0771</v>
+        <v>-0.0142</v>
       </c>
       <c r="V8" t="n">
-        <v>1.881</v>
+        <v>-1.7384</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6745</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1067</v>
+        <v>2.2715</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3246</v>
+        <v>-2.109</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2179</v>
+        <v>4.3805</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1854</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7511</v>
+        <v>-0.6503</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4343</v>
+        <v>0.5609</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5003</v>
+        <v>-1.8839</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6101</v>
+        <v>-1.8942</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8901</v>
+        <v>0.0102</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6851</v>
+        <v>1.7945</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1409</v>
+        <v>1.2439</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5442</v>
+        <v>0.5507</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.0509</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.8097</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.8097</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.1338</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.1757</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.0419</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.7384</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.7384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8025</v>
+        <v>1.7121</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4378</v>
+        <v>1.6286</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2402</v>
+        <v>0.0835</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08939999999999999</v>
+        <v>1.638</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6503</v>
+        <v>0.3271</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5609</v>
+        <v>1.3109</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8839</v>
+        <v>0.9383</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8942</v>
+        <v>0.4436</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0102</v>
+        <v>0.4947</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7945</v>
+        <v>0.6997</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2439</v>
+        <v>-0.1165</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5507</v>
+        <v>0.8162</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>2.579</v>
+        <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.513</v>
+        <v>0.1417</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3797</v>
+        <v>0.2098</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1333</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8097</v>
+        <v>-0.266</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8097</v>
+        <v>1.4724</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2836</v>
+        <v>1.4508</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4245</v>
+        <v>2.9867</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1409</v>
+        <v>-1.5359</v>
       </c>
       <c r="G11" t="n">
-        <v>1.638</v>
+        <v>1.8734</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3271</v>
+        <v>1.784</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3109</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9383</v>
+        <v>2.6636</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4436</v>
+        <v>2.5807</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4947</v>
+        <v>0.0829</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6997</v>
+        <v>-0.7902</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1165</v>
+        <v>-0.7967</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8162</v>
+        <v>0.0065</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2868</v>
+        <v>0.7369</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0057</v>
+        <v>0.3232</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2925</v>
+        <v>0.4137</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.266</v>
+        <v>-2.9449</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7384</v>
+        <v>-2.9449</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.117</v>
+        <v>0.958</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8153</v>
+        <v>-1.9367</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6983</v>
+        <v>2.8947</v>
       </c>
       <c r="G12" t="n">
         <v>0.2788</v>
@@ -1390,13 +1390,13 @@
         <v>3.1741</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3201</v>
+        <v>-0.2451</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6744</v>
+        <v>0.2041</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.4493</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3777</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7653</v>
+        <v>-1.8867</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3875</v>
+        <v>2.7803</v>
       </c>
       <c r="G13" t="n">
         <v>0.6009</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6369</v>
+        <v>-0.3656</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6744</v>
+        <v>0.2041</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9625</v>
+        <v>-0.5697</v>
       </c>
       <c r="V13" t="n">
         <v>-0.532</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>46.3956</v>
+        <v>47.0188</v>
       </c>
       <c r="E14" t="n">
-        <v>21.6915</v>
+        <v>22.3151</v>
       </c>
       <c r="F14" t="n">
         <v>24.7038</v>
@@ -1546,16 +1546,16 @@
         <v>24.798</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5667000000000002</v>
+        <v>1.1901</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1549</v>
+        <v>2.7782</v>
       </c>
       <c r="U14" t="n">
         <v>-1.588</v>
       </c>
       <c r="V14" t="n">
-        <v>3.035200000000001</v>
+        <v>3.0352</v>
       </c>
       <c r="W14" t="n">
         <v>10.6443</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0879</v>
+        <v>-2.0999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.753</v>
+        <v>-0.9571</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3349</v>
+        <v>-1.1428</v>
       </c>
       <c r="G15" t="n">
         <v>-1.612</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0873</v>
+        <v>-0.0992</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5896</v>
+        <v>0.3855</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6768</v>
+        <v>-0.4847</v>
       </c>
       <c r="V15" t="n">
         <v>0.6032</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.2585</v>
+        <v>-3.0766</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3657</v>
+        <v>-1.2637</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8928</v>
+        <v>-1.8129</v>
       </c>
       <c r="G16" t="n">
         <v>-2.1276</v>
@@ -1702,13 +1702,13 @@
         <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4682</v>
+        <v>-0.2863</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.102</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3662</v>
+        <v>-0.2863</v>
       </c>
       <c r="V16" t="n">
         <v>-0.266</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.6647</v>
+        <v>-3.1129</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3517</v>
+        <v>-0.7396</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.313</v>
+        <v>-2.3733</v>
       </c>
       <c r="G17" t="n">
         <v>-5.0682</v>
@@ -1780,13 +1780,13 @@
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.216</v>
+        <v>0.3359</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1699</v>
+        <v>0.4422</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.046</v>
+        <v>-0.1064</v>
       </c>
       <c r="V17" t="n">
         <v>2.4129</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0787</v>
+        <v>-3.5547</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.3623</v>
+        <v>2.1174</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2836</v>
+        <v>-5.6721</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.5261</v>
+        <v>-3.4825</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.4341</v>
+        <v>-0.7761</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.092</v>
+        <v>-2.7064</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.2899</v>
+        <v>1.4501</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.3702</v>
+        <v>2.1679</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0803</v>
+        <v>-0.7178</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2362</v>
+        <v>-4.9326</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0639</v>
+        <v>-2.944</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1723</v>
+        <v>-1.9886</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1822</v>
+        <v>-1.3887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8398</v>
+        <v>-0.1317</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3119</v>
+        <v>0.3175</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5279</v>
+        <v>-0.4493</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.3373</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.7384</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.3411</v>
+        <v>-4.4241</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0437</v>
+        <v>-3.2156</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2974</v>
+        <v>-1.2085</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-3.2365</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2668</v>
+        <v>-1.9553</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1827</v>
+        <v>-1.2812</v>
       </c>
       <c r="J19" t="n">
-        <v>0.575</v>
+        <v>-1.9346</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5348000000000001</v>
+        <v>-1.2946</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>-0.64</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.659</v>
+        <v>-1.3018</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8016</v>
+        <v>-0.6607</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1425</v>
+        <v>-0.6412</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.3725</v>
+        <v>0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3725</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>0.322</v>
+        <v>-0.5087</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7539</v>
+        <v>-0.289</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4319</v>
+        <v>-0.2197</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3705</v>
+        <v>-4.4789</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9095</v>
+        <v>-2.3498</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.461</v>
+        <v>-2.1291</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2365</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9553</v>
+        <v>-0.2668</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2812</v>
+        <v>0.1827</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9346</v>
+        <v>0.575</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2946</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.64</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3018</v>
+        <v>-0.659</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6607</v>
+        <v>-0.8016</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6412</v>
+        <v>0.1425</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7935</v>
+        <v>-3.3725</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-3.3725</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4551</v>
+        <v>0.1842</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0171</v>
+        <v>0.4478</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4722</v>
+        <v>-0.2636</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4755</v>
+        <v>-5.0683</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5052</v>
+        <v>-4.5664</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.9807</v>
+        <v>-0.5019</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4825</v>
+        <v>-5.5261</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7761</v>
+        <v>-4.4341</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7064</v>
+        <v>-1.092</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4501</v>
+        <v>-3.2899</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1679</v>
+        <v>-3.3702</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7178</v>
+        <v>0.0803</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.9326</v>
+        <v>-2.2362</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.944</v>
+        <v>-1.0639</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9886</v>
+        <v>-1.1723</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3968</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3887</v>
+        <v>-2.1822</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0525</v>
+        <v>0.8502</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2946</v>
+        <v>0.1078</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7579</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3373</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7384</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8581</v>
+        <v>-5.2939</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5032</v>
+        <v>-3.2148</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.355</v>
+        <v>-2.0792</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4998</v>
+        <v>-4.2105</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1161</v>
+        <v>-0.2668</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3837</v>
+        <v>-3.9437</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0799</v>
+        <v>-1.3711</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3997</v>
+        <v>0.1825</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6802</v>
+        <v>-1.5535</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.42</v>
+        <v>-2.8395</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7165</v>
+        <v>-0.4493</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7035</v>
+        <v>-2.3902</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3968</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2089</v>
+        <v>-0.5044</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0521</v>
+        <v>-0.289</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1568</v>
+        <v>-0.2155</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.964</v>
+        <v>1.2065</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.4916</v>
+        <v>2.4129</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1544</v>
+        <v>-6.4591</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8269</v>
+        <v>-4.9316</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3274</v>
+        <v>-1.5275</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.2105</v>
+        <v>-4.4998</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2668</v>
+        <v>-2.1161</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.9437</v>
+        <v>-2.3837</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3711</v>
+        <v>-2.0799</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1825</v>
+        <v>-1.3997</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5535</v>
+        <v>-0.6802</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8395</v>
+        <v>-2.42</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4493</v>
+        <v>-0.7165</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.3902</v>
+        <v>-1.7035</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3649</v>
+        <v>0.6079</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9011</v>
+        <v>0.6237</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4637</v>
+        <v>-0.0157</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2065</v>
+        <v>-2.964</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4129</v>
+        <v>-1.4916</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.106</v>
+        <v>-8.1469</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0929</v>
+        <v>-5.5828</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.013</v>
+        <v>-2.5641</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0271</v>
@@ -2326,13 +2326,13 @@
         <v>2.1822</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2934</v>
+        <v>-0.3344</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6687</v>
+        <v>-0.1586</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6247</v>
+        <v>-0.1758</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8097</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-46.3954</v>
+        <v>-45.71530000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-24.7037</v>
+        <v>-24.704</v>
       </c>
       <c r="F25" t="n">
-        <v>-21.6916</v>
+        <v>-21.0114</v>
       </c>
       <c r="G25" t="n">
-        <v>-32.8744</v>
+        <v>-32.87439999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-15.5468</v>
@@ -2377,7 +2377,7 @@
         <v>-17.3275</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.102899999999998</v>
+        <v>-9.1029</v>
       </c>
       <c r="K25" t="n">
         <v>-3.5964</v>
@@ -2404,13 +2404,13 @@
         <v>14.8788</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5667</v>
+        <v>0.1135</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5883</v>
+        <v>1.5879</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.1547</v>
+        <v>-1.4746</v>
       </c>
       <c r="V25" t="n">
         <v>-3.0354</v>
